--- a/strategy.xlsx
+++ b/strategy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Beurteilen</t>
   </si>
@@ -97,18 +97,6 @@
   </si>
   <si>
     <t xml:space="preserve">Outcome based compensation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get outsourced work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auxilliaries for large projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complicated and small projects</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -153,19 +141,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,74 +688,74 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="33.350000000000001" customHeight="1">
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" ht="33.350000000000001" customHeight="1">
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" ht="33.350000000000001" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -781,10 +763,10 @@
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -795,36 +777,22 @@
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="2"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="C13" s="2"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
